--- a/Daten/data_slido.xlsx
+++ b/Daten/data_slido.xlsx
@@ -55,13 +55,13 @@
     <t xml:space="preserve">https://app.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ</t>
   </si>
   <si>
+    <t xml:space="preserve">www.jef-bayern.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://app.sli.do/event/geV2Mhwjr214EoiLePvBLu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www.jef-bayern.de</t>
   </si>
   <si>
     <t xml:space="preserve">Nürnberg</t>
@@ -188,12 +188,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -454,150 +458,150 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="50.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="47.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="48.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="50.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="47.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="45.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -605,8 +609,8 @@
     <hyperlink ref="B2" r:id="rId1" display="https://app.sli.do/event/obRbSvykRMTii7BHz5Kdxj"/>
     <hyperlink ref="C2" r:id="rId2" display="https://app.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx"/>
     <hyperlink ref="D2" r:id="rId3" display="https://app.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ"/>
-    <hyperlink ref="E2" r:id="rId4" display="https://app.sli.do/event/geV2Mhwjr214EoiLePvBLu"/>
-    <hyperlink ref="F2" r:id="rId5" display="https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1"/>
+    <hyperlink ref="F2" r:id="rId4" display="https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1"/>
+    <hyperlink ref="G2" r:id="rId5" display="https://app.sli.do/event/geV2Mhwjr214EoiLePvBLu"/>
     <hyperlink ref="B3" r:id="rId6" display="https://app.sli.do/event/igq3HyvzFLzkZURA7ceLCC"/>
     <hyperlink ref="C3" r:id="rId7" display="https://app.sli.do/event/cGu8QCMc789wmmh8Vc2Fya"/>
     <hyperlink ref="D3" r:id="rId8" display="https://app.sli.do/event/eHfbbWUUfx46oVaXFytCFZ"/>

--- a/Daten/data_slido.xlsx
+++ b/Daten/data_slido.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="6"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\JEF\SimEP\Daten\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1FA3FA-0866-4778-A627-51DABAE541E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Übersicht" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Übersicht" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,104 +27,86 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
-    <t xml:space="preserve">Stadt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PfE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/obRbSvykRMTii7BHz5Kdxj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www.jef-bayern.de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/geV2Mhwjr214EoiLePvBLu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nürnberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/igq3HyvzFLzkZURA7ceLCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/cGu8QCMc789wmmh8Vc2Fya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/eHfbbWUUfx46oVaXFytCFZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/dtWESWtajaF2nmnxngxbg4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.sli.do/event/gtxWrkTKz8if2RfFpJ69xd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">München</t>
+    <t>Stadt</t>
+  </si>
+  <si>
+    <t>EVP</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>PfE</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>www.jef-bayern.de</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Coburg</t>
+  </si>
+  <si>
+    <t>Passau</t>
+  </si>
+  <si>
+    <t>München</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/cGu8QCMc789wmmh8Vc2Fya</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/eHfbbWUUfx46oVaXFytCFZ</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/dtWESWtajaF2nmnxngxbg4</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/obRbSvykRMTii7BHz5Kdxj</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/igq3HyvzFLzkZURA7ceLCC</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/geV2Mhwjr214EoiLePvBLu</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/gtxWrkTKz8if2RfFpJ69xd</t>
+  </si>
+  <si>
+    <t>https://wall.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -129,7 +116,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -152,7 +139,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -160,61 +147,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -273,13 +220,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -321,12 +284,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -358,7 +321,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -382,7 +345,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -442,187 +405,181 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="50.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="47.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="45.4"/>
+    <col min="1" max="1" width="9.3984375" customWidth="1"/>
+    <col min="2" max="2" width="47.1328125" customWidth="1"/>
+    <col min="3" max="4" width="50.1328125" customWidth="1"/>
+    <col min="5" max="5" width="47.53125" customWidth="1"/>
+    <col min="6" max="6" width="48.3984375" customWidth="1"/>
+    <col min="7" max="7" width="45.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://app.sli.do/event/obRbSvykRMTii7BHz5Kdxj"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://app.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx"/>
-    <hyperlink ref="D2" r:id="rId3" display="https://app.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ"/>
-    <hyperlink ref="F2" r:id="rId4" display="https://app.sli.do/event/tFRDNiRPzWnazRZebU57n1"/>
-    <hyperlink ref="G2" r:id="rId5" display="https://app.sli.do/event/geV2Mhwjr214EoiLePvBLu"/>
-    <hyperlink ref="B3" r:id="rId6" display="https://app.sli.do/event/igq3HyvzFLzkZURA7ceLCC"/>
-    <hyperlink ref="C3" r:id="rId7" display="https://app.sli.do/event/cGu8QCMc789wmmh8Vc2Fya"/>
-    <hyperlink ref="D3" r:id="rId8" display="https://app.sli.do/event/eHfbbWUUfx46oVaXFytCFZ"/>
-    <hyperlink ref="E3" r:id="rId9" display="https://app.sli.do/event/dtWESWtajaF2nmnxngxbg4"/>
-    <hyperlink ref="F3" r:id="rId10" display="https://app.sli.do/event/gtxWrkTKz8if2RfFpJ69xd"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G2" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E3" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>